--- a/public/exports/55133018.xlsx
+++ b/public/exports/55133018.xlsx
@@ -14574,7 +14574,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015127</t>
+          <t xml:space="preserve">200015126</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015972</t>
+          <t xml:space="preserve">200015973</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015975</t>
+          <t xml:space="preserve">200015973</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015976</t>
+          <t xml:space="preserve">200015973</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041402</t>
+          <t xml:space="preserve">200041412</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041413</t>
+          <t xml:space="preserve">200041412</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041402</t>
+          <t xml:space="preserve">200041412</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -18174,7 +18174,7 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041413</t>
+          <t xml:space="preserve">200041412</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">310005708</t>
+          <t xml:space="preserve">310005703</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
@@ -22254,7 +22254,7 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t xml:space="preserve">311182448</t>
+          <t xml:space="preserve">311182450</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
@@ -22314,7 +22314,7 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t xml:space="preserve">311182449</t>
+          <t xml:space="preserve">311182450</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
@@ -26274,7 +26274,7 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278564</t>
+          <t xml:space="preserve">311278563</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -26394,7 +26394,7 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278566</t>
+          <t xml:space="preserve">311278563</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -27114,7 +27114,7 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308498</t>
+          <t xml:space="preserve">311308497</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308498</t>
+          <t xml:space="preserve">311308497</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -27234,7 +27234,7 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308498</t>
+          <t xml:space="preserve">311308497</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308498</t>
+          <t xml:space="preserve">311308497</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -27414,7 +27414,7 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308498</t>
+          <t xml:space="preserve">311308497</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t xml:space="preserve">311563326</t>
+          <t xml:space="preserve">311563316</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
@@ -32454,7 +32454,7 @@
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t xml:space="preserve">311682738</t>
+          <t xml:space="preserve">311682737</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
@@ -32514,7 +32514,7 @@
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t xml:space="preserve">311682736</t>
+          <t xml:space="preserve">311682737</t>
         </is>
       </c>
       <c r="J542" t="inlineStr">
@@ -35814,7 +35814,7 @@
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t xml:space="preserve">311792250</t>
+          <t xml:space="preserve">311741738</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
@@ -40074,7 +40074,7 @@
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t xml:space="preserve">311778513</t>
+          <t xml:space="preserve">311778511</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
@@ -40134,7 +40134,7 @@
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t xml:space="preserve">311778513</t>
+          <t xml:space="preserve">311778511</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
@@ -40194,7 +40194,7 @@
       </c>
       <c r="I670" t="inlineStr">
         <is>
-          <t xml:space="preserve">311778513</t>
+          <t xml:space="preserve">311778511</t>
         </is>
       </c>
       <c r="J670" t="inlineStr">
@@ -46914,7 +46914,7 @@
       </c>
       <c r="I782" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818725</t>
+          <t xml:space="preserve">311818722</t>
         </is>
       </c>
       <c r="J782" t="inlineStr">
@@ -46974,7 +46974,7 @@
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818723</t>
+          <t xml:space="preserve">311818722</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
@@ -47034,7 +47034,7 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818723</t>
+          <t xml:space="preserve">311818722</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
@@ -47094,7 +47094,7 @@
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818723</t>
+          <t xml:space="preserve">311818722</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">

--- a/public/exports/55133018.xlsx
+++ b/public/exports/55133018.xlsx
@@ -15719,12 +15719,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014900</t>
+          <t xml:space="preserve">200014898</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015127</t>
+          <t xml:space="preserve">200015126</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015121</t>
+          <t xml:space="preserve">200015119</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015640</t>
+          <t xml:space="preserve">200015637</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -16954,12 +16954,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015973</t>
+          <t xml:space="preserve">200015971</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lokalenergi Handel A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -17409,7 +17409,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017090</t>
+          <t xml:space="preserve">200017089</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -18904,7 +18904,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028425</t>
+          <t xml:space="preserve">200028422</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">310005706</t>
+          <t xml:space="preserve">310005703</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
@@ -20724,7 +20724,7 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">310005708</t>
+          <t xml:space="preserve">310005703</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
@@ -20789,7 +20789,7 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">310005706</t>
+          <t xml:space="preserve">310005703</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">310005706</t>
+          <t xml:space="preserve">310005703</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
@@ -26184,7 +26184,7 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216674</t>
+          <t xml:space="preserve">311216671</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
@@ -26249,7 +26249,7 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216674</t>
+          <t xml:space="preserve">311216671</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
@@ -26314,7 +26314,7 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216674</t>
+          <t xml:space="preserve">311216671</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -26379,7 +26379,7 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216674</t>
+          <t xml:space="preserve">311216671</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
@@ -26444,7 +26444,7 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216674</t>
+          <t xml:space="preserve">311216671</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
@@ -26509,7 +26509,7 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216674</t>
+          <t xml:space="preserve">311216671</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
@@ -26574,7 +26574,7 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216674</t>
+          <t xml:space="preserve">311216671</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
@@ -26639,7 +26639,7 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216674</t>
+          <t xml:space="preserve">311216671</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -26704,7 +26704,7 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216674</t>
+          <t xml:space="preserve">311216671</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
@@ -26769,7 +26769,7 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216674</t>
+          <t xml:space="preserve">311216671</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216674</t>
+          <t xml:space="preserve">311216671</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
@@ -26899,7 +26899,7 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216674</t>
+          <t xml:space="preserve">311216671</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216674</t>
+          <t xml:space="preserve">311216671</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
@@ -28459,12 +28459,12 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278564</t>
+          <t xml:space="preserve">311278563</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K438" t="inlineStr">
@@ -32294,7 +32294,7 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t xml:space="preserve">311563326</t>
+          <t xml:space="preserve">311563316</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
@@ -35219,7 +35219,7 @@
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t xml:space="preserve">311682737</t>
+          <t xml:space="preserve">311682736</t>
         </is>
       </c>
       <c r="J542" t="inlineStr">
@@ -38664,7 +38664,7 @@
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t xml:space="preserve">311792242</t>
+          <t xml:space="preserve">311741738</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
@@ -38729,7 +38729,7 @@
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t xml:space="preserve">311792242</t>
+          <t xml:space="preserve">311741738</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
@@ -47179,12 +47179,12 @@
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797110</t>
+          <t xml:space="preserve">311797108</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K726" t="inlineStr">
@@ -47244,12 +47244,12 @@
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797109</t>
+          <t xml:space="preserve">311797108</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K727" t="inlineStr">
@@ -47309,12 +47309,12 @@
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797110</t>
+          <t xml:space="preserve">311797108</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K728" t="inlineStr">
@@ -47374,12 +47374,12 @@
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797110</t>
+          <t xml:space="preserve">311797108</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K729" t="inlineStr">
@@ -47439,12 +47439,12 @@
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797110</t>
+          <t xml:space="preserve">311797108</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K730" t="inlineStr">
@@ -47504,12 +47504,12 @@
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797110</t>
+          <t xml:space="preserve">311797108</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K731" t="inlineStr">
@@ -47569,12 +47569,12 @@
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797110</t>
+          <t xml:space="preserve">311797108</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K732" t="inlineStr">
@@ -47634,12 +47634,12 @@
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797110</t>
+          <t xml:space="preserve">311797108</t>
         </is>
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K733" t="inlineStr">
@@ -47699,12 +47699,12 @@
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797110</t>
+          <t xml:space="preserve">311797108</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K734" t="inlineStr">
@@ -47764,12 +47764,12 @@
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797110</t>
+          <t xml:space="preserve">311797108</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K735" t="inlineStr">
@@ -47829,12 +47829,12 @@
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797110</t>
+          <t xml:space="preserve">311797108</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K736" t="inlineStr">
@@ -50819,12 +50819,12 @@
       </c>
       <c r="I782" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818725</t>
+          <t xml:space="preserve">311818722</t>
         </is>
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K782" t="inlineStr">
@@ -50884,12 +50884,12 @@
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818723</t>
+          <t xml:space="preserve">311818722</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K783" t="inlineStr">
@@ -50949,12 +50949,12 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818723</t>
+          <t xml:space="preserve">311818722</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K784" t="inlineStr">
@@ -51014,12 +51014,12 @@
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818723</t>
+          <t xml:space="preserve">311818722</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K785" t="inlineStr">
@@ -53029,12 +53029,12 @@
       </c>
       <c r="I816" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833629</t>
+          <t xml:space="preserve">311833627</t>
         </is>
       </c>
       <c r="J816" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K816" t="inlineStr">
@@ -53094,12 +53094,12 @@
       </c>
       <c r="I817" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833629</t>
+          <t xml:space="preserve">311833627</t>
         </is>
       </c>
       <c r="J817" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K817" t="inlineStr">
@@ -53159,12 +53159,12 @@
       </c>
       <c r="I818" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833629</t>
+          <t xml:space="preserve">311833627</t>
         </is>
       </c>
       <c r="J818" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K818" t="inlineStr">
@@ -53224,12 +53224,12 @@
       </c>
       <c r="I819" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833629</t>
+          <t xml:space="preserve">311833627</t>
         </is>
       </c>
       <c r="J819" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K819" t="inlineStr">
@@ -53289,12 +53289,12 @@
       </c>
       <c r="I820" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833629</t>
+          <t xml:space="preserve">311833627</t>
         </is>
       </c>
       <c r="J820" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K820" t="inlineStr">
@@ -53354,12 +53354,12 @@
       </c>
       <c r="I821" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833629</t>
+          <t xml:space="preserve">311833627</t>
         </is>
       </c>
       <c r="J821" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K821" t="inlineStr">
@@ -53419,12 +53419,12 @@
       </c>
       <c r="I822" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833629</t>
+          <t xml:space="preserve">311833627</t>
         </is>
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K822" t="inlineStr">
@@ -53484,12 +53484,12 @@
       </c>
       <c r="I823" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833629</t>
+          <t xml:space="preserve">311833627</t>
         </is>
       </c>
       <c r="J823" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K823" t="inlineStr">
@@ -53549,12 +53549,12 @@
       </c>
       <c r="I824" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833629</t>
+          <t xml:space="preserve">311833627</t>
         </is>
       </c>
       <c r="J824" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K824" t="inlineStr">
@@ -53614,12 +53614,12 @@
       </c>
       <c r="I825" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833629</t>
+          <t xml:space="preserve">311833627</t>
         </is>
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K825" t="inlineStr">
